--- a/www/terminologies/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/www/terminologies/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14761" uniqueCount="9863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14872" uniqueCount="9937">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260827120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-08-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4877</t>
+    <t>4914</t>
   </si>
   <si>
     <t>Code</t>
@@ -1993,6 +1993,204 @@
     <t>AASA/A6/P4/21</t>
   </si>
   <si>
+    <t>30024</t>
+  </si>
+  <si>
+    <t>AASA/A8/76/00</t>
+  </si>
+  <si>
+    <t>30025</t>
+  </si>
+  <si>
+    <t>AASA/A8/09/00</t>
+  </si>
+  <si>
+    <t>30026</t>
+  </si>
+  <si>
+    <t>AASA/A8/10/00</t>
+  </si>
+  <si>
+    <t>30027</t>
+  </si>
+  <si>
+    <t>AASA/A9/76/00</t>
+  </si>
+  <si>
+    <t>30028</t>
+  </si>
+  <si>
+    <t>AASA/A9/09/00</t>
+  </si>
+  <si>
+    <t>30029</t>
+  </si>
+  <si>
+    <t>AASA/A9/10/00</t>
+  </si>
+  <si>
+    <t>30030</t>
+  </si>
+  <si>
+    <t>AASA/B0/09/00</t>
+  </si>
+  <si>
+    <t>30031</t>
+  </si>
+  <si>
+    <t>AASA/B0/10/00</t>
+  </si>
+  <si>
+    <t>30032</t>
+  </si>
+  <si>
+    <t>AASA/B1/09/00</t>
+  </si>
+  <si>
+    <t>30033</t>
+  </si>
+  <si>
+    <t>AASA/B1/10/00</t>
+  </si>
+  <si>
+    <t>30034</t>
+  </si>
+  <si>
+    <t>AASA/C1/09/00</t>
+  </si>
+  <si>
+    <t>30035</t>
+  </si>
+  <si>
+    <t>AASA/C1/10/00</t>
+  </si>
+  <si>
+    <t>30036</t>
+  </si>
+  <si>
+    <t>AASA/C1/76/00</t>
+  </si>
+  <si>
+    <t>30037</t>
+  </si>
+  <si>
+    <t>AASA/C3/09/00</t>
+  </si>
+  <si>
+    <t>30038</t>
+  </si>
+  <si>
+    <t>AASA/C3/10/00</t>
+  </si>
+  <si>
+    <t>30039</t>
+  </si>
+  <si>
+    <t>AASA/C3/76/00</t>
+  </si>
+  <si>
+    <t>30040</t>
+  </si>
+  <si>
+    <t>AASA/D1/09/00</t>
+  </si>
+  <si>
+    <t>30041</t>
+  </si>
+  <si>
+    <t>AASA/D1/10/00</t>
+  </si>
+  <si>
+    <t>30042</t>
+  </si>
+  <si>
+    <t>AASA/D1/76/00</t>
+  </si>
+  <si>
+    <t>30043</t>
+  </si>
+  <si>
+    <t>AASA/F4/09/00</t>
+  </si>
+  <si>
+    <t>30044</t>
+  </si>
+  <si>
+    <t>AASA/F4/10/00</t>
+  </si>
+  <si>
+    <t>30045</t>
+  </si>
+  <si>
+    <t>AASA/F4/76/00</t>
+  </si>
+  <si>
+    <t>30046</t>
+  </si>
+  <si>
+    <t>AASA/F9/09/00</t>
+  </si>
+  <si>
+    <t>30047</t>
+  </si>
+  <si>
+    <t>AASA/F9/10/00</t>
+  </si>
+  <si>
+    <t>30048</t>
+  </si>
+  <si>
+    <t>AASA/F9/76/00</t>
+  </si>
+  <si>
+    <t>30049</t>
+  </si>
+  <si>
+    <t>AASA/H2/09/00</t>
+  </si>
+  <si>
+    <t>30050</t>
+  </si>
+  <si>
+    <t>AASA/H2/10/00</t>
+  </si>
+  <si>
+    <t>30051</t>
+  </si>
+  <si>
+    <t>AASA/H2/76/00</t>
+  </si>
+  <si>
+    <t>30052</t>
+  </si>
+  <si>
+    <t>AASA/H3/09/00</t>
+  </si>
+  <si>
+    <t>30053</t>
+  </si>
+  <si>
+    <t>AASA/H3/10/00</t>
+  </si>
+  <si>
+    <t>30054</t>
+  </si>
+  <si>
+    <t>AASA/H3/76/00</t>
+  </si>
+  <si>
+    <t>30055</t>
+  </si>
+  <si>
+    <t>AASA/S8/00/00</t>
+  </si>
+  <si>
+    <t>30056</t>
+  </si>
+  <si>
+    <t>AASA/03/05/08</t>
+  </si>
+  <si>
     <t>40001</t>
   </si>
   <si>
@@ -29603,6 +29801,30 @@
   </si>
   <si>
     <t>ASOCR/960/11/811</t>
+  </si>
+  <si>
+    <t>81061</t>
+  </si>
+  <si>
+    <t>ASOCR/246/21/824</t>
+  </si>
+  <si>
+    <t>81062</t>
+  </si>
+  <si>
+    <t>ASOCR/246/21/835</t>
+  </si>
+  <si>
+    <t>81063</t>
+  </si>
+  <si>
+    <t>ASOCR/247/21/824</t>
+  </si>
+  <si>
+    <t>81064</t>
+  </si>
+  <si>
+    <t>ASOCR/247/21/835</t>
   </si>
 </sst>
 </file>
@@ -30232,7 +30454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4878"/>
+  <dimension ref="A1:D4915"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -88773,6 +88995,450 @@
       </c>
       <c r="D4878" s="2"/>
     </row>
+    <row r="4879">
+      <c r="A4879" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4879" t="s" s="2">
+        <v>9863</v>
+      </c>
+      <c r="C4879" t="s" s="2">
+        <v>9864</v>
+      </c>
+      <c r="D4879" s="2"/>
+    </row>
+    <row r="4880">
+      <c r="A4880" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4880" t="s" s="2">
+        <v>9865</v>
+      </c>
+      <c r="C4880" t="s" s="2">
+        <v>9866</v>
+      </c>
+      <c r="D4880" s="2"/>
+    </row>
+    <row r="4881">
+      <c r="A4881" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4881" t="s" s="2">
+        <v>9867</v>
+      </c>
+      <c r="C4881" t="s" s="2">
+        <v>9868</v>
+      </c>
+      <c r="D4881" s="2"/>
+    </row>
+    <row r="4882">
+      <c r="A4882" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4882" t="s" s="2">
+        <v>9869</v>
+      </c>
+      <c r="C4882" t="s" s="2">
+        <v>9870</v>
+      </c>
+      <c r="D4882" s="2"/>
+    </row>
+    <row r="4883">
+      <c r="A4883" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4883" t="s" s="2">
+        <v>9871</v>
+      </c>
+      <c r="C4883" t="s" s="2">
+        <v>9872</v>
+      </c>
+      <c r="D4883" s="2"/>
+    </row>
+    <row r="4884">
+      <c r="A4884" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4884" t="s" s="2">
+        <v>9873</v>
+      </c>
+      <c r="C4884" t="s" s="2">
+        <v>9874</v>
+      </c>
+      <c r="D4884" s="2"/>
+    </row>
+    <row r="4885">
+      <c r="A4885" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4885" t="s" s="2">
+        <v>9875</v>
+      </c>
+      <c r="C4885" t="s" s="2">
+        <v>9876</v>
+      </c>
+      <c r="D4885" s="2"/>
+    </row>
+    <row r="4886">
+      <c r="A4886" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4886" t="s" s="2">
+        <v>9877</v>
+      </c>
+      <c r="C4886" t="s" s="2">
+        <v>9878</v>
+      </c>
+      <c r="D4886" s="2"/>
+    </row>
+    <row r="4887">
+      <c r="A4887" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4887" t="s" s="2">
+        <v>9879</v>
+      </c>
+      <c r="C4887" t="s" s="2">
+        <v>9880</v>
+      </c>
+      <c r="D4887" s="2"/>
+    </row>
+    <row r="4888">
+      <c r="A4888" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4888" t="s" s="2">
+        <v>9881</v>
+      </c>
+      <c r="C4888" t="s" s="2">
+        <v>9882</v>
+      </c>
+      <c r="D4888" s="2"/>
+    </row>
+    <row r="4889">
+      <c r="A4889" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4889" t="s" s="2">
+        <v>9883</v>
+      </c>
+      <c r="C4889" t="s" s="2">
+        <v>9884</v>
+      </c>
+      <c r="D4889" s="2"/>
+    </row>
+    <row r="4890">
+      <c r="A4890" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4890" t="s" s="2">
+        <v>9885</v>
+      </c>
+      <c r="C4890" t="s" s="2">
+        <v>9886</v>
+      </c>
+      <c r="D4890" s="2"/>
+    </row>
+    <row r="4891">
+      <c r="A4891" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4891" t="s" s="2">
+        <v>9887</v>
+      </c>
+      <c r="C4891" t="s" s="2">
+        <v>9888</v>
+      </c>
+      <c r="D4891" s="2"/>
+    </row>
+    <row r="4892">
+      <c r="A4892" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4892" t="s" s="2">
+        <v>9889</v>
+      </c>
+      <c r="C4892" t="s" s="2">
+        <v>9890</v>
+      </c>
+      <c r="D4892" s="2"/>
+    </row>
+    <row r="4893">
+      <c r="A4893" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4893" t="s" s="2">
+        <v>9891</v>
+      </c>
+      <c r="C4893" t="s" s="2">
+        <v>9892</v>
+      </c>
+      <c r="D4893" s="2"/>
+    </row>
+    <row r="4894">
+      <c r="A4894" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4894" t="s" s="2">
+        <v>9893</v>
+      </c>
+      <c r="C4894" t="s" s="2">
+        <v>9894</v>
+      </c>
+      <c r="D4894" s="2"/>
+    </row>
+    <row r="4895">
+      <c r="A4895" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4895" t="s" s="2">
+        <v>9895</v>
+      </c>
+      <c r="C4895" t="s" s="2">
+        <v>9896</v>
+      </c>
+      <c r="D4895" s="2"/>
+    </row>
+    <row r="4896">
+      <c r="A4896" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4896" t="s" s="2">
+        <v>9897</v>
+      </c>
+      <c r="C4896" t="s" s="2">
+        <v>9898</v>
+      </c>
+      <c r="D4896" s="2"/>
+    </row>
+    <row r="4897">
+      <c r="A4897" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4897" t="s" s="2">
+        <v>9899</v>
+      </c>
+      <c r="C4897" t="s" s="2">
+        <v>9900</v>
+      </c>
+      <c r="D4897" s="2"/>
+    </row>
+    <row r="4898">
+      <c r="A4898" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4898" t="s" s="2">
+        <v>9901</v>
+      </c>
+      <c r="C4898" t="s" s="2">
+        <v>9902</v>
+      </c>
+      <c r="D4898" s="2"/>
+    </row>
+    <row r="4899">
+      <c r="A4899" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4899" t="s" s="2">
+        <v>9903</v>
+      </c>
+      <c r="C4899" t="s" s="2">
+        <v>9904</v>
+      </c>
+      <c r="D4899" s="2"/>
+    </row>
+    <row r="4900">
+      <c r="A4900" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4900" t="s" s="2">
+        <v>9905</v>
+      </c>
+      <c r="C4900" t="s" s="2">
+        <v>9906</v>
+      </c>
+      <c r="D4900" s="2"/>
+    </row>
+    <row r="4901">
+      <c r="A4901" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4901" t="s" s="2">
+        <v>9907</v>
+      </c>
+      <c r="C4901" t="s" s="2">
+        <v>9908</v>
+      </c>
+      <c r="D4901" s="2"/>
+    </row>
+    <row r="4902">
+      <c r="A4902" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4902" t="s" s="2">
+        <v>9909</v>
+      </c>
+      <c r="C4902" t="s" s="2">
+        <v>9910</v>
+      </c>
+      <c r="D4902" s="2"/>
+    </row>
+    <row r="4903">
+      <c r="A4903" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4903" t="s" s="2">
+        <v>9911</v>
+      </c>
+      <c r="C4903" t="s" s="2">
+        <v>9912</v>
+      </c>
+      <c r="D4903" s="2"/>
+    </row>
+    <row r="4904">
+      <c r="A4904" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4904" t="s" s="2">
+        <v>9913</v>
+      </c>
+      <c r="C4904" t="s" s="2">
+        <v>9914</v>
+      </c>
+      <c r="D4904" s="2"/>
+    </row>
+    <row r="4905">
+      <c r="A4905" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4905" t="s" s="2">
+        <v>9915</v>
+      </c>
+      <c r="C4905" t="s" s="2">
+        <v>9916</v>
+      </c>
+      <c r="D4905" s="2"/>
+    </row>
+    <row r="4906">
+      <c r="A4906" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4906" t="s" s="2">
+        <v>9917</v>
+      </c>
+      <c r="C4906" t="s" s="2">
+        <v>9918</v>
+      </c>
+      <c r="D4906" s="2"/>
+    </row>
+    <row r="4907">
+      <c r="A4907" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4907" t="s" s="2">
+        <v>9919</v>
+      </c>
+      <c r="C4907" t="s" s="2">
+        <v>9920</v>
+      </c>
+      <c r="D4907" s="2"/>
+    </row>
+    <row r="4908">
+      <c r="A4908" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4908" t="s" s="2">
+        <v>9921</v>
+      </c>
+      <c r="C4908" t="s" s="2">
+        <v>9922</v>
+      </c>
+      <c r="D4908" s="2"/>
+    </row>
+    <row r="4909">
+      <c r="A4909" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4909" t="s" s="2">
+        <v>9923</v>
+      </c>
+      <c r="C4909" t="s" s="2">
+        <v>9924</v>
+      </c>
+      <c r="D4909" s="2"/>
+    </row>
+    <row r="4910">
+      <c r="A4910" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4910" t="s" s="2">
+        <v>9925</v>
+      </c>
+      <c r="C4910" t="s" s="2">
+        <v>9926</v>
+      </c>
+      <c r="D4910" s="2"/>
+    </row>
+    <row r="4911">
+      <c r="A4911" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4911" t="s" s="2">
+        <v>9927</v>
+      </c>
+      <c r="C4911" t="s" s="2">
+        <v>9928</v>
+      </c>
+      <c r="D4911" s="2"/>
+    </row>
+    <row r="4912">
+      <c r="A4912" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4912" t="s" s="2">
+        <v>9929</v>
+      </c>
+      <c r="C4912" t="s" s="2">
+        <v>9930</v>
+      </c>
+      <c r="D4912" s="2"/>
+    </row>
+    <row r="4913">
+      <c r="A4913" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4913" t="s" s="2">
+        <v>9931</v>
+      </c>
+      <c r="C4913" t="s" s="2">
+        <v>9932</v>
+      </c>
+      <c r="D4913" s="2"/>
+    </row>
+    <row r="4914">
+      <c r="A4914" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4914" t="s" s="2">
+        <v>9933</v>
+      </c>
+      <c r="C4914" t="s" s="2">
+        <v>9934</v>
+      </c>
+      <c r="D4914" s="2"/>
+    </row>
+    <row r="4915">
+      <c r="A4915" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4915" t="s" s="2">
+        <v>9935</v>
+      </c>
+      <c r="C4915" t="s" s="2">
+        <v>9936</v>
+      </c>
+      <c r="D4915" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/terminologies/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/www/terminologies/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14872" uniqueCount="9937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14893" uniqueCount="9951">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260827120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4914</t>
+    <t>4921</t>
   </si>
   <si>
     <t>Code</t>
@@ -23459,6 +23459,48 @@
   </si>
   <si>
     <t>AMSR/965/43/700</t>
+  </si>
+  <si>
+    <t>72537</t>
+  </si>
+  <si>
+    <t>AMSR/508/11/840</t>
+  </si>
+  <si>
+    <t>72538</t>
+  </si>
+  <si>
+    <t>AMSR/508/11/841</t>
+  </si>
+  <si>
+    <t>72539</t>
+  </si>
+  <si>
+    <t>AMSR/508/16/841</t>
+  </si>
+  <si>
+    <t>72540</t>
+  </si>
+  <si>
+    <t>AMSR/570/11/441</t>
+  </si>
+  <si>
+    <t>72541</t>
+  </si>
+  <si>
+    <t>AMSR/570/40/441</t>
+  </si>
+  <si>
+    <t>72542</t>
+  </si>
+  <si>
+    <t>AMSR/962/11/441</t>
+  </si>
+  <si>
+    <t>72543</t>
+  </si>
+  <si>
+    <t>AMSR/962/40/441</t>
   </si>
   <si>
     <t>80001</t>
@@ -30454,7 +30496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4915"/>
+  <dimension ref="A1:D4922"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -89439,6 +89481,90 @@
       </c>
       <c r="D4915" s="2"/>
     </row>
+    <row r="4916">
+      <c r="A4916" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4916" t="s" s="2">
+        <v>9937</v>
+      </c>
+      <c r="C4916" t="s" s="2">
+        <v>9938</v>
+      </c>
+      <c r="D4916" s="2"/>
+    </row>
+    <row r="4917">
+      <c r="A4917" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4917" t="s" s="2">
+        <v>9939</v>
+      </c>
+      <c r="C4917" t="s" s="2">
+        <v>9940</v>
+      </c>
+      <c r="D4917" s="2"/>
+    </row>
+    <row r="4918">
+      <c r="A4918" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4918" t="s" s="2">
+        <v>9941</v>
+      </c>
+      <c r="C4918" t="s" s="2">
+        <v>9942</v>
+      </c>
+      <c r="D4918" s="2"/>
+    </row>
+    <row r="4919">
+      <c r="A4919" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4919" t="s" s="2">
+        <v>9943</v>
+      </c>
+      <c r="C4919" t="s" s="2">
+        <v>9944</v>
+      </c>
+      <c r="D4919" s="2"/>
+    </row>
+    <row r="4920">
+      <c r="A4920" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4920" t="s" s="2">
+        <v>9945</v>
+      </c>
+      <c r="C4920" t="s" s="2">
+        <v>9946</v>
+      </c>
+      <c r="D4920" s="2"/>
+    </row>
+    <row r="4921">
+      <c r="A4921" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4921" t="s" s="2">
+        <v>9947</v>
+      </c>
+      <c r="C4921" t="s" s="2">
+        <v>9948</v>
+      </c>
+      <c r="D4921" s="2"/>
+    </row>
+    <row r="4922">
+      <c r="A4922" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B4922" t="s" s="2">
+        <v>9949</v>
+      </c>
+      <c r="C4922" t="s" s="2">
+        <v>9950</v>
+      </c>
+      <c r="D4922" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
